--- a/uploads/询价单_7.xlsx
+++ b/uploads/询价单_7.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,12 @@
     <font>
       <name val="微软雅黑"/>
       <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
@@ -64,7 +70,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -78,7 +84,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,27 +144,56 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -524,6 +574,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -554,6 +608,15 @@
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="3" t="n"/>
       <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="3" t="n"/>
+      <c r="W3" s="3" t="n"/>
+      <c r="X3" s="3" t="n"/>
+      <c r="Y3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -563,7 +626,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>XJ-202609-0002</t>
+          <t>XJ-202609-0006</t>
         </is>
       </c>
       <c r="C4" s="6" t="n"/>
@@ -574,7 +637,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>111111111</t>
+          <t>办公</t>
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
@@ -588,6 +651,15 @@
       <c r="N4" s="6" t="n"/>
       <c r="O4" s="6" t="n"/>
       <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="n"/>
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="6" t="n"/>
+      <c r="T4" s="6" t="n"/>
+      <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -597,7 +669,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>WX2026090102</t>
+          <t>ZH2026090401</t>
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
@@ -608,7 +680,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>111111111</t>
+          <t>办公</t>
         </is>
       </c>
       <c r="F5" s="6" t="n"/>
@@ -622,6 +694,15 @@
       <c r="N5" s="6" t="n"/>
       <c r="O5" s="6" t="n"/>
       <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="6" t="n"/>
+      <c r="R5" s="6" t="n"/>
+      <c r="S5" s="6" t="n"/>
+      <c r="T5" s="6" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -631,7 +712,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>维修车间</t>
+          <t>综合办</t>
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
@@ -642,7 +723,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>邢果</t>
+          <t>温丽</t>
         </is>
       </c>
       <c r="F6" s="6" t="n"/>
@@ -656,6 +737,15 @@
       <c r="N6" s="6" t="n"/>
       <c r="O6" s="6" t="n"/>
       <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+      <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="n"/>
+      <c r="Y6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -665,7 +755,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 17:37:09</t>
+          <t>2026-09-04 08:35:55</t>
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
@@ -690,6 +780,15 @@
       <c r="N7" s="6" t="n"/>
       <c r="O7" s="6" t="n"/>
       <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -710,7 +809,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>2 家</t>
+          <t>3 家</t>
         </is>
       </c>
       <c r="F8" s="6" t="n"/>
@@ -724,6 +823,15 @@
       <c r="N8" s="6" t="n"/>
       <c r="O8" s="6" t="n"/>
       <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="n"/>
+      <c r="T8" s="6" t="n"/>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -746,6 +854,15 @@
       <c r="N11" s="3" t="n"/>
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="3" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -768,162 +885,337 @@
           <t>规格型号</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>山西昂拓贸易有限公司 含税单价</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>山西昂拓贸易有限公司 总价（含税含运）</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>山西昂拓贸易有限公司 品牌</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>山西昂拓贸易有限公司 交付</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>山西昂拓贸易有限公司 质保</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>山西昂拓贸易有限公司 厂家备注</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>山西利百加 含税单价</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>山西利百加 总价（含税含运）</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>山西利百加 品牌</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>山西利百加 交付</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>山西利百加 质保</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>山西利百加 厂家备注</t>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>山西同程科技有限公司 含税单价</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>山西同程科技有限公司 总价（含税含运）</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>山西同程科技有限公司 品牌</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>山西同程科技有限公司 交付</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>山西同程科技有限公司 质保</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>山西同程科技有限公司 厂家备注</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>山西同程科技有限公司 厂家原始报价</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>河曲县郭雄水泵经销处 含税单价</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>河曲县郭雄水泵经销处 总价（含税含运）</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>河曲县郭雄水泵经销处 品牌</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t>河曲县郭雄水泵经销处 交付</t>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>河曲县郭雄水泵经销处 质保</t>
+        </is>
+      </c>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>河曲县郭雄水泵经销处 厂家备注</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>河曲县郭雄水泵经销处 厂家原始报价</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>郑州金恒电子技术有限公司 含税单价</t>
+        </is>
+      </c>
+      <c r="T12" s="10" t="inlineStr">
+        <is>
+          <t>郑州金恒电子技术有限公司 总价（含税含运）</t>
+        </is>
+      </c>
+      <c r="U12" s="10" t="inlineStr">
+        <is>
+          <t>郑州金恒电子技术有限公司 品牌</t>
+        </is>
+      </c>
+      <c r="V12" s="10" t="inlineStr">
+        <is>
+          <t>郑州金恒电子技术有限公司 交付</t>
+        </is>
+      </c>
+      <c r="W12" s="10" t="inlineStr">
+        <is>
+          <t>郑州金恒电子技术有限公司 质保</t>
+        </is>
+      </c>
+      <c r="X12" s="10" t="inlineStr">
+        <is>
+          <t>郑州金恒电子技术有限公司 厂家备注</t>
+        </is>
+      </c>
+      <c r="Y12" s="10" t="inlineStr">
+        <is>
+          <t>郑州金恒电子技术有限公司 厂家原始报价</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>11111</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>1个</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>10个</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>★4,000.00</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>40,000.00</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>府谷</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>7天</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>3个月</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr"/>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>40,000.00</t>
+        </is>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>5,600.00</t>
+        </is>
+      </c>
+      <c r="M13" s="15" t="inlineStr">
+        <is>
+          <t>56,000.00</t>
+        </is>
+      </c>
+      <c r="N13" s="15" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>★10.00</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr"/>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="8" t="inlineStr"/>
-      <c r="P13" s="8" t="inlineStr"/>
+      <c r="O13" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P13" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q13" s="15" t="inlineStr"/>
+      <c r="R13" s="15" t="inlineStr">
+        <is>
+          <t>56,000.00</t>
+        </is>
+      </c>
+      <c r="S13" s="16" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="T13" s="17" t="inlineStr">
+        <is>
+          <t>50,000.00</t>
+        </is>
+      </c>
+      <c r="U13" s="17" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="V13" s="17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W13" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X13" s="17" t="inlineStr"/>
+      <c r="Y13" s="17" t="inlineStr">
+        <is>
+          <t>50,000.00</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>11111</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>1个</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>★10.00</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
-      <c r="O14" s="8" t="inlineStr"/>
-      <c r="P14" s="8" t="inlineStr"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>mac键盘</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>15个</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>300*200</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>2,250.00</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>府谷</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>7天</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>3个月</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr"/>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>2,250.00</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>★60.00</t>
+        </is>
+      </c>
+      <c r="M14" s="15" t="inlineStr">
+        <is>
+          <t>900.00</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="O14" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P14" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q14" s="15" t="inlineStr"/>
+      <c r="R14" s="15" t="inlineStr">
+        <is>
+          <t>900.00</t>
+        </is>
+      </c>
+      <c r="S14" s="16" t="inlineStr">
+        <is>
+          <t>120.00</t>
+        </is>
+      </c>
+      <c r="T14" s="17" t="inlineStr">
+        <is>
+          <t>1,800.00</t>
+        </is>
+      </c>
+      <c r="U14" s="17" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="V14" s="17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W14" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X14" s="17" t="inlineStr"/>
+      <c r="Y14" s="17" t="inlineStr">
+        <is>
+          <t>1,800.00</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr"/>
@@ -934,26 +1226,36 @@
       </c>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="13" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>42,250.00</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="20" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="M15" s="6" t="inlineStr"/>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>56,900.00</t>
+        </is>
+      </c>
+      <c r="O15" s="22" t="n"/>
+      <c r="P15" s="22" t="n"/>
+      <c r="Q15" s="22" t="n"/>
+      <c r="R15" s="22" t="n"/>
+      <c r="T15" s="6" t="inlineStr"/>
+      <c r="U15" s="23" t="inlineStr">
+        <is>
+          <t>51,800.00</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="24" t="n"/>
+      <c r="X15" s="24" t="n"/>
+      <c r="Y15" s="25" t="inlineStr">
         <is>
           <t>★=该项最低价</t>
         </is>
@@ -980,227 +1282,391 @@
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n"/>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="3" t="n"/>
+      <c r="W17" s="3" t="n"/>
+      <c r="X17" s="3" t="n"/>
+      <c r="Y17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>本批次采购已收到多家供应商报价，正在定标审批中，待领导确认后确定合作方。
 【品牌对比】
-山西昂拓贸易有限公司报价¥200.00：未填写品牌
-山西利百加报价¥100.00：未填写品牌
+山西同程科技有限公司报价¥42,250.00：府谷
+河曲县郭雄水泵经销处报价¥57,000.00：11；111
+郑州金恒电子技术有限公司报价¥51,800.00：555
 【总价（含税含运）】
-山西昂拓贸易有限公司：总价（含税含运） ¥200.00
-山西利百加：总价（含税含运） ¥100.00</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="15" t="n"/>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="15" t="n"/>
-      <c r="P18" s="15" t="n"/>
+山西同程科技有限公司：总价（含税含运） ¥42,250.00
+河曲县郭雄水泵经销处：总价（含税含运） ¥57,000.00
+郑州金恒电子技术有限公司：总价（含税含运） ¥51,800.00</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="24" t="n"/>
+      <c r="H18" s="24" t="n"/>
+      <c r="I18" s="24" t="n"/>
+      <c r="J18" s="24" t="n"/>
+      <c r="K18" s="24" t="n"/>
+      <c r="L18" s="24" t="n"/>
+      <c r="M18" s="24" t="n"/>
+      <c r="N18" s="24" t="n"/>
+      <c r="O18" s="24" t="n"/>
+      <c r="P18" s="24" t="n"/>
+      <c r="Q18" s="24" t="n"/>
+      <c r="R18" s="24" t="n"/>
+      <c r="S18" s="24" t="n"/>
+      <c r="T18" s="24" t="n"/>
+      <c r="U18" s="24" t="n"/>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="24" t="n"/>
+      <c r="X18" s="24" t="n"/>
+      <c r="Y18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="15" t="n"/>
-      <c r="L19" s="15" t="n"/>
-      <c r="M19" s="15" t="n"/>
-      <c r="N19" s="15" t="n"/>
-      <c r="O19" s="15" t="n"/>
-      <c r="P19" s="15" t="n"/>
+      <c r="A19" s="24" t="n"/>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="24" t="n"/>
+      <c r="I19" s="24" t="n"/>
+      <c r="J19" s="24" t="n"/>
+      <c r="K19" s="24" t="n"/>
+      <c r="L19" s="24" t="n"/>
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="24" t="n"/>
+      <c r="O19" s="24" t="n"/>
+      <c r="P19" s="24" t="n"/>
+      <c r="Q19" s="24" t="n"/>
+      <c r="R19" s="24" t="n"/>
+      <c r="S19" s="24" t="n"/>
+      <c r="T19" s="24" t="n"/>
+      <c r="U19" s="24" t="n"/>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="24" t="n"/>
+      <c r="X19" s="24" t="n"/>
+      <c r="Y19" s="24" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="15" t="n"/>
-      <c r="L20" s="15" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="15" t="n"/>
-      <c r="P20" s="15" t="n"/>
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="24" t="n"/>
+      <c r="G20" s="24" t="n"/>
+      <c r="H20" s="24" t="n"/>
+      <c r="I20" s="24" t="n"/>
+      <c r="J20" s="24" t="n"/>
+      <c r="K20" s="24" t="n"/>
+      <c r="L20" s="24" t="n"/>
+      <c r="M20" s="24" t="n"/>
+      <c r="N20" s="24" t="n"/>
+      <c r="O20" s="24" t="n"/>
+      <c r="P20" s="24" t="n"/>
+      <c r="Q20" s="24" t="n"/>
+      <c r="R20" s="24" t="n"/>
+      <c r="S20" s="24" t="n"/>
+      <c r="T20" s="24" t="n"/>
+      <c r="U20" s="24" t="n"/>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="24" t="n"/>
+      <c r="X20" s="24" t="n"/>
+      <c r="Y20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
-      <c r="K21" s="15" t="n"/>
-      <c r="L21" s="15" t="n"/>
-      <c r="M21" s="15" t="n"/>
-      <c r="N21" s="15" t="n"/>
-      <c r="O21" s="15" t="n"/>
-      <c r="P21" s="15" t="n"/>
+      <c r="A21" s="24" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="n"/>
+      <c r="I21" s="24" t="n"/>
+      <c r="J21" s="24" t="n"/>
+      <c r="K21" s="24" t="n"/>
+      <c r="L21" s="24" t="n"/>
+      <c r="M21" s="24" t="n"/>
+      <c r="N21" s="24" t="n"/>
+      <c r="O21" s="24" t="n"/>
+      <c r="P21" s="24" t="n"/>
+      <c r="Q21" s="24" t="n"/>
+      <c r="R21" s="24" t="n"/>
+      <c r="S21" s="24" t="n"/>
+      <c r="T21" s="24" t="n"/>
+      <c r="U21" s="24" t="n"/>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="24" t="n"/>
+      <c r="X21" s="24" t="n"/>
+      <c r="Y21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n"/>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="15" t="n"/>
-      <c r="L22" s="15" t="n"/>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="15" t="n"/>
+      <c r="A22" s="24" t="n"/>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="24" t="n"/>
+      <c r="H22" s="24" t="n"/>
+      <c r="I22" s="24" t="n"/>
+      <c r="J22" s="24" t="n"/>
+      <c r="K22" s="24" t="n"/>
+      <c r="L22" s="24" t="n"/>
+      <c r="M22" s="24" t="n"/>
+      <c r="N22" s="24" t="n"/>
+      <c r="O22" s="24" t="n"/>
+      <c r="P22" s="24" t="n"/>
+      <c r="Q22" s="24" t="n"/>
+      <c r="R22" s="24" t="n"/>
+      <c r="S22" s="24" t="n"/>
+      <c r="T22" s="24" t="n"/>
+      <c r="U22" s="24" t="n"/>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="24" t="n"/>
+      <c r="X22" s="24" t="n"/>
+      <c r="Y22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n"/>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
-      <c r="K23" s="15" t="n"/>
-      <c r="L23" s="15" t="n"/>
-      <c r="M23" s="15" t="n"/>
-      <c r="N23" s="15" t="n"/>
-      <c r="O23" s="15" t="n"/>
-      <c r="P23" s="15" t="n"/>
+      <c r="A23" s="24" t="n"/>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="24" t="n"/>
+      <c r="I23" s="24" t="n"/>
+      <c r="J23" s="24" t="n"/>
+      <c r="K23" s="24" t="n"/>
+      <c r="L23" s="24" t="n"/>
+      <c r="M23" s="24" t="n"/>
+      <c r="N23" s="24" t="n"/>
+      <c r="O23" s="24" t="n"/>
+      <c r="P23" s="24" t="n"/>
+      <c r="Q23" s="24" t="n"/>
+      <c r="R23" s="24" t="n"/>
+      <c r="S23" s="24" t="n"/>
+      <c r="T23" s="24" t="n"/>
+      <c r="U23" s="24" t="n"/>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="24" t="n"/>
+      <c r="X23" s="24" t="n"/>
+      <c r="Y23" s="24" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n"/>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
-      <c r="K24" s="15" t="n"/>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="15" t="n"/>
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="24" t="n"/>
+      <c r="J24" s="24" t="n"/>
+      <c r="K24" s="24" t="n"/>
+      <c r="L24" s="24" t="n"/>
+      <c r="M24" s="24" t="n"/>
+      <c r="N24" s="24" t="n"/>
+      <c r="O24" s="24" t="n"/>
+      <c r="P24" s="24" t="n"/>
+      <c r="Q24" s="24" t="n"/>
+      <c r="R24" s="24" t="n"/>
+      <c r="S24" s="24" t="n"/>
+      <c r="T24" s="24" t="n"/>
+      <c r="U24" s="24" t="n"/>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="24" t="n"/>
+      <c r="X24" s="24" t="n"/>
+      <c r="Y24" s="24" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n"/>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
-      <c r="H25" s="15" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="n"/>
-      <c r="K25" s="15" t="n"/>
-      <c r="L25" s="15" t="n"/>
-      <c r="M25" s="15" t="n"/>
-      <c r="N25" s="15" t="n"/>
-      <c r="O25" s="15" t="n"/>
-      <c r="P25" s="15" t="n"/>
+      <c r="A25" s="24" t="n"/>
+      <c r="B25" s="24" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="24" t="n"/>
+      <c r="I25" s="24" t="n"/>
+      <c r="J25" s="24" t="n"/>
+      <c r="K25" s="24" t="n"/>
+      <c r="L25" s="24" t="n"/>
+      <c r="M25" s="24" t="n"/>
+      <c r="N25" s="24" t="n"/>
+      <c r="O25" s="24" t="n"/>
+      <c r="P25" s="24" t="n"/>
+      <c r="Q25" s="24" t="n"/>
+      <c r="R25" s="24" t="n"/>
+      <c r="S25" s="24" t="n"/>
+      <c r="T25" s="24" t="n"/>
+      <c r="U25" s="24" t="n"/>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="24" t="n"/>
+      <c r="X25" s="24" t="n"/>
+      <c r="Y25" s="24" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n"/>
-      <c r="K26" s="15" t="n"/>
-      <c r="L26" s="15" t="n"/>
-      <c r="M26" s="15" t="n"/>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="15" t="n"/>
-      <c r="P26" s="15" t="n"/>
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
+      <c r="I26" s="24" t="n"/>
+      <c r="J26" s="24" t="n"/>
+      <c r="K26" s="24" t="n"/>
+      <c r="L26" s="24" t="n"/>
+      <c r="M26" s="24" t="n"/>
+      <c r="N26" s="24" t="n"/>
+      <c r="O26" s="24" t="n"/>
+      <c r="P26" s="24" t="n"/>
+      <c r="Q26" s="24" t="n"/>
+      <c r="R26" s="24" t="n"/>
+      <c r="S26" s="24" t="n"/>
+      <c r="T26" s="24" t="n"/>
+      <c r="U26" s="24" t="n"/>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="24" t="n"/>
+      <c r="X26" s="24" t="n"/>
+      <c r="Y26" s="24" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n"/>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="15" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="15" t="n"/>
-      <c r="L27" s="15" t="n"/>
-      <c r="M27" s="15" t="n"/>
-      <c r="N27" s="15" t="n"/>
-      <c r="O27" s="15" t="n"/>
-      <c r="P27" s="15" t="n"/>
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="24" t="n"/>
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="24" t="n"/>
+      <c r="K27" s="24" t="n"/>
+      <c r="L27" s="24" t="n"/>
+      <c r="M27" s="24" t="n"/>
+      <c r="N27" s="24" t="n"/>
+      <c r="O27" s="24" t="n"/>
+      <c r="P27" s="24" t="n"/>
+      <c r="Q27" s="24" t="n"/>
+      <c r="R27" s="24" t="n"/>
+      <c r="S27" s="24" t="n"/>
+      <c r="T27" s="24" t="n"/>
+      <c r="U27" s="24" t="n"/>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="24" t="n"/>
+      <c r="X27" s="24" t="n"/>
+      <c r="Y27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
-      <c r="K28" s="15" t="n"/>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="n"/>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="15" t="n"/>
-      <c r="P28" s="15" t="n"/>
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="24" t="n"/>
+      <c r="I28" s="24" t="n"/>
+      <c r="J28" s="24" t="n"/>
+      <c r="K28" s="24" t="n"/>
+      <c r="L28" s="24" t="n"/>
+      <c r="M28" s="24" t="n"/>
+      <c r="N28" s="24" t="n"/>
+      <c r="O28" s="24" t="n"/>
+      <c r="P28" s="24" t="n"/>
+      <c r="Q28" s="24" t="n"/>
+      <c r="R28" s="24" t="n"/>
+      <c r="S28" s="24" t="n"/>
+      <c r="T28" s="24" t="n"/>
+      <c r="U28" s="24" t="n"/>
+      <c r="V28" s="24" t="n"/>
+      <c r="W28" s="24" t="n"/>
+      <c r="X28" s="24" t="n"/>
+      <c r="Y28" s="24" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
+      <c r="I29" s="24" t="n"/>
+      <c r="J29" s="24" t="n"/>
+      <c r="K29" s="24" t="n"/>
+      <c r="L29" s="24" t="n"/>
+      <c r="M29" s="24" t="n"/>
+      <c r="N29" s="24" t="n"/>
+      <c r="O29" s="24" t="n"/>
+      <c r="P29" s="24" t="n"/>
+      <c r="Q29" s="24" t="n"/>
+      <c r="R29" s="24" t="n"/>
+      <c r="S29" s="24" t="n"/>
+      <c r="T29" s="24" t="n"/>
+      <c r="U29" s="24" t="n"/>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="24" t="n"/>
+      <c r="X29" s="24" t="n"/>
+      <c r="Y29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="n"/>
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="24" t="n"/>
+      <c r="K30" s="24" t="n"/>
+      <c r="L30" s="24" t="n"/>
+      <c r="M30" s="24" t="n"/>
+      <c r="N30" s="24" t="n"/>
+      <c r="O30" s="24" t="n"/>
+      <c r="P30" s="24" t="n"/>
+      <c r="Q30" s="24" t="n"/>
+      <c r="R30" s="24" t="n"/>
+      <c r="S30" s="24" t="n"/>
+      <c r="T30" s="24" t="n"/>
+      <c r="U30" s="24" t="n"/>
+      <c r="V30" s="24" t="n"/>
+      <c r="W30" s="24" t="n"/>
+      <c r="X30" s="24" t="n"/>
+      <c r="Y30" s="24" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>编制人：</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>审核人：</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G31" s="27" t="inlineStr">
         <is>
           <t>日期：</t>
         </is>
@@ -1208,20 +1674,20 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E4:P4"/>
-    <mergeCell ref="E7:P7"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:P6"/>
-    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="E4:Y4"/>
+    <mergeCell ref="A11:Y11"/>
+    <mergeCell ref="E6:Y6"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A1:P1"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A17:P17"/>
-    <mergeCell ref="A18:P28"/>
-    <mergeCell ref="E5:P5"/>
-    <mergeCell ref="E8:P8"/>
-    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="E7:Y7"/>
+    <mergeCell ref="A18:Y30"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="E5:Y5"/>
+    <mergeCell ref="A17:Y17"/>
+    <mergeCell ref="E8:Y8"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A3:Y3"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
